--- a/data/삼성전자.xlsx
+++ b/data/삼성전자.xlsx
@@ -510,16 +510,16 @@
         <v>45659</v>
       </c>
       <c r="B4" t="n">
-        <v>52526.6328125</v>
+        <v>52526.62890625</v>
       </c>
       <c r="C4" t="n">
-        <v>52723.36177434457</v>
+        <v>52723.35785346442</v>
       </c>
       <c r="D4" t="n">
-        <v>51444.62352235487</v>
+        <v>51444.61969657069</v>
       </c>
       <c r="E4" t="n">
-        <v>51838.08144604401</v>
+        <v>51838.07759099953</v>
       </c>
       <c r="F4" t="n">
         <v>16630538</v>
@@ -530,16 +530,16 @@
         <v>45660</v>
       </c>
       <c r="B5" t="n">
-        <v>53510.28125</v>
+        <v>53510.27734375</v>
       </c>
       <c r="C5" t="n">
-        <v>54198.83266314338</v>
+        <v>54198.82870662914</v>
       </c>
       <c r="D5" t="n">
-        <v>51936.44944852941</v>
+        <v>51936.44565716912</v>
       </c>
       <c r="E5" t="n">
-        <v>51936.44944852941</v>
+        <v>51936.44565716912</v>
       </c>
       <c r="F5" t="n">
         <v>19318046</v>
@@ -550,16 +550,16 @@
         <v>45663</v>
       </c>
       <c r="B6" t="n">
-        <v>54985.75</v>
+        <v>54985.74609375</v>
       </c>
       <c r="C6" t="n">
-        <v>55280.84347048301</v>
+        <v>55280.83954326923</v>
       </c>
       <c r="D6" t="n">
-        <v>53411.91815742398</v>
+        <v>53411.91436298077</v>
       </c>
       <c r="E6" t="n">
-        <v>53510.28264758497</v>
+        <v>53510.27884615384</v>
       </c>
       <c r="F6" t="n">
         <v>19034284</v>
@@ -570,16 +570,16 @@
         <v>45664</v>
       </c>
       <c r="B7" t="n">
-        <v>54493.92578125</v>
+        <v>54493.921875</v>
       </c>
       <c r="C7" t="n">
-        <v>56362.85103367554</v>
+        <v>56362.84699345668</v>
       </c>
       <c r="D7" t="n">
-        <v>54493.92578125</v>
+        <v>54493.921875</v>
       </c>
       <c r="E7" t="n">
-        <v>55871.02859882671</v>
+        <v>55871.02459386281</v>
       </c>
       <c r="F7" t="n">
         <v>17030235</v>
@@ -590,16 +590,16 @@
         <v>45665</v>
       </c>
       <c r="B8" t="n">
-        <v>56362.84765625</v>
+        <v>56362.8515625</v>
       </c>
       <c r="C8" t="n">
-        <v>56559.57661840096</v>
+        <v>56559.58053828534</v>
       </c>
       <c r="D8" t="n">
-        <v>53805.37114828752</v>
+        <v>53805.37487729057</v>
       </c>
       <c r="E8" t="n">
-        <v>53903.735629363</v>
+        <v>53903.73936518325</v>
       </c>
       <c r="F8" t="n">
         <v>26593553</v>
@@ -630,16 +630,16 @@
         <v>45667</v>
       </c>
       <c r="B10" t="n">
-        <v>54395.55859375</v>
+        <v>54395.5625</v>
       </c>
       <c r="C10" t="n">
-        <v>55575.93237878616</v>
+        <v>55575.93636980109</v>
       </c>
       <c r="D10" t="n">
-        <v>54297.19411166365</v>
+        <v>54297.19801084991</v>
       </c>
       <c r="E10" t="n">
-        <v>55182.47445044078</v>
+        <v>55182.47841320073</v>
       </c>
       <c r="F10" t="n">
         <v>16059223</v>
@@ -650,16 +650,16 @@
         <v>45670</v>
       </c>
       <c r="B11" t="n">
-        <v>53215.1875</v>
+        <v>53215.18359375</v>
       </c>
       <c r="C11" t="n">
-        <v>54100.46788354898</v>
+        <v>54100.46391231516</v>
       </c>
       <c r="D11" t="n">
-        <v>53215.1875</v>
+        <v>53215.18359375</v>
       </c>
       <c r="E11" t="n">
-        <v>53707.00993530499</v>
+        <v>53707.00599295287</v>
       </c>
       <c r="F11" t="n">
         <v>16868600</v>
@@ -710,16 +710,16 @@
         <v>45673</v>
       </c>
       <c r="B14" t="n">
-        <v>53411.91796875</v>
+        <v>53411.9140625</v>
       </c>
       <c r="C14" t="n">
-        <v>54100.46939744475</v>
+        <v>54100.46544083794</v>
       </c>
       <c r="D14" t="n">
-        <v>53215.18898912293</v>
+        <v>53215.18509726059</v>
       </c>
       <c r="E14" t="n">
-        <v>53313.55347893647</v>
+        <v>53313.54957988029</v>
       </c>
       <c r="F14" t="n">
         <v>18627298</v>
@@ -750,16 +750,16 @@
         <v>45677</v>
       </c>
       <c r="B16" t="n">
-        <v>52526.6328125</v>
+        <v>52526.62890625</v>
       </c>
       <c r="C16" t="n">
-        <v>53018.45521711143</v>
+        <v>53018.45127428605</v>
       </c>
       <c r="D16" t="n">
-        <v>52428.26833157772</v>
+        <v>52428.26443264279</v>
       </c>
       <c r="E16" t="n">
-        <v>52723.36177434457</v>
+        <v>52723.35785346442</v>
       </c>
       <c r="F16" t="n">
         <v>11822531</v>
@@ -790,16 +790,16 @@
         <v>45679</v>
       </c>
       <c r="B18" t="n">
-        <v>53411.91796875</v>
+        <v>53411.9140625</v>
       </c>
       <c r="C18" t="n">
-        <v>53510.28245856354</v>
+        <v>53510.27854511971</v>
       </c>
       <c r="D18" t="n">
-        <v>52231.54409098757</v>
+        <v>52231.54027106354</v>
       </c>
       <c r="E18" t="n">
-        <v>52526.63756042818</v>
+        <v>52526.63371892265</v>
       </c>
       <c r="F18" t="n">
         <v>18341991</v>
@@ -890,16 +890,16 @@
         <v>45692</v>
       </c>
       <c r="B23" t="n">
-        <v>51838.08203125</v>
+        <v>51838.0859375</v>
       </c>
       <c r="C23" t="n">
-        <v>52723.36236954459</v>
+        <v>52723.36634250474</v>
       </c>
       <c r="D23" t="n">
-        <v>50657.70824685721</v>
+        <v>50657.71206416034</v>
       </c>
       <c r="E23" t="n">
-        <v>50756.07272888994</v>
+        <v>50756.07655360531</v>
       </c>
       <c r="F23" t="n">
         <v>27214851</v>
@@ -910,16 +910,16 @@
         <v>45693</v>
       </c>
       <c r="B24" t="n">
-        <v>52034.8125</v>
+        <v>52034.80859375</v>
       </c>
       <c r="C24" t="n">
-        <v>52920.09286389414</v>
+        <v>52920.0888911862</v>
       </c>
       <c r="D24" t="n">
-        <v>51936.44801512288</v>
+        <v>51936.44411625709</v>
       </c>
       <c r="E24" t="n">
-        <v>52723.36389413989</v>
+        <v>52723.35993620037</v>
       </c>
       <c r="F24" t="n">
         <v>15974885</v>
@@ -970,16 +970,16 @@
         <v>45698</v>
       </c>
       <c r="B27" t="n">
-        <v>54690.65625</v>
+        <v>54690.65234375</v>
       </c>
       <c r="C27" t="n">
-        <v>54985.74971897482</v>
+        <v>54985.74579164793</v>
       </c>
       <c r="D27" t="n">
-        <v>52034.81502922661</v>
+        <v>52034.81131266861</v>
       </c>
       <c r="E27" t="n">
-        <v>52133.17951888489</v>
+        <v>52133.17579530126</v>
       </c>
       <c r="F27" t="n">
         <v>27577591</v>
@@ -990,16 +990,16 @@
         <v>45699</v>
       </c>
       <c r="B28" t="n">
-        <v>54789.01953125</v>
+        <v>54789.015625</v>
       </c>
       <c r="C28" t="n">
-        <v>55379.20645618268</v>
+        <v>55379.20250785458</v>
       </c>
       <c r="D28" t="n">
-        <v>54100.46811882855</v>
+        <v>54100.46426166966</v>
       </c>
       <c r="E28" t="n">
-        <v>54592.29055627244</v>
+        <v>54592.28666404847</v>
       </c>
       <c r="F28" t="n">
         <v>24596196</v>
@@ -1050,16 +1050,16 @@
         <v>45702</v>
       </c>
       <c r="B31" t="n">
-        <v>55084.11328125</v>
+        <v>55084.109375</v>
       </c>
       <c r="C31" t="n">
-        <v>56362.85162527901</v>
+        <v>56362.84762834821</v>
       </c>
       <c r="D31" t="n">
-        <v>55084.11328125</v>
+        <v>55084.109375</v>
       </c>
       <c r="E31" t="n">
-        <v>55084.11328125</v>
+        <v>55084.109375</v>
       </c>
       <c r="F31" t="n">
         <v>23979779</v>
@@ -1070,16 +1070,16 @@
         <v>45705</v>
       </c>
       <c r="B32" t="n">
-        <v>55084.11328125</v>
+        <v>55084.109375</v>
       </c>
       <c r="C32" t="n">
-        <v>55575.93572126116</v>
+        <v>55575.93178013393</v>
       </c>
       <c r="D32" t="n">
-        <v>54789.0198172433</v>
+        <v>54789.01593191964</v>
       </c>
       <c r="E32" t="n">
-        <v>55182.47776925223</v>
+        <v>55182.47385602679</v>
       </c>
       <c r="F32" t="n">
         <v>11916027</v>
@@ -1090,16 +1090,16 @@
         <v>45706</v>
       </c>
       <c r="B33" t="n">
-        <v>55969.390625</v>
+        <v>55969.38671875</v>
       </c>
       <c r="C33" t="n">
-        <v>56264.48407293497</v>
+        <v>56264.48014608963</v>
       </c>
       <c r="D33" t="n">
-        <v>54985.74579855009</v>
+        <v>54985.74196095123</v>
       </c>
       <c r="E33" t="n">
-        <v>55280.83924648506</v>
+        <v>55280.83538829086</v>
       </c>
       <c r="F33" t="n">
         <v>22131007</v>
@@ -1130,16 +1130,16 @@
         <v>45708</v>
       </c>
       <c r="B35" t="n">
-        <v>57444.859375</v>
+        <v>57444.85546875</v>
       </c>
       <c r="C35" t="n">
-        <v>58133.41077161815</v>
+        <v>58133.40681854666</v>
       </c>
       <c r="D35" t="n">
-        <v>57149.7659193065</v>
+        <v>57149.76203312286</v>
       </c>
       <c r="E35" t="n">
-        <v>58133.41077161815</v>
+        <v>58133.40681854666</v>
       </c>
       <c r="F35" t="n">
         <v>21589059</v>
@@ -1150,16 +1150,16 @@
         <v>45709</v>
       </c>
       <c r="B36" t="n">
-        <v>57248.12890625</v>
+        <v>57248.1328125</v>
       </c>
       <c r="C36" t="n">
-        <v>57543.22235422036</v>
+        <v>57543.22628060567</v>
       </c>
       <c r="D36" t="n">
-        <v>56166.11959702535</v>
+        <v>56166.12342944587</v>
       </c>
       <c r="E36" t="n">
-        <v>57444.85787156357</v>
+        <v>57444.86179123711</v>
       </c>
       <c r="F36" t="n">
         <v>22198428</v>
@@ -1170,16 +1170,16 @@
         <v>45712</v>
       </c>
       <c r="B37" t="n">
-        <v>56362.84765625</v>
+        <v>56362.8515625</v>
       </c>
       <c r="C37" t="n">
-        <v>56756.30558055192</v>
+        <v>56756.30951407068</v>
       </c>
       <c r="D37" t="n">
-        <v>56264.48317517452</v>
+        <v>56264.48707460733</v>
       </c>
       <c r="E37" t="n">
-        <v>56362.84765625</v>
+        <v>56362.8515625</v>
       </c>
       <c r="F37" t="n">
         <v>14138471</v>
@@ -1310,16 +1310,16 @@
         <v>45722</v>
       </c>
       <c r="B44" t="n">
-        <v>53411.91796875</v>
+        <v>53411.9140625</v>
       </c>
       <c r="C44" t="n">
-        <v>53608.64694837707</v>
+        <v>53608.64302773941</v>
       </c>
       <c r="D44" t="n">
-        <v>53116.8244993094</v>
+        <v>53116.82061464088</v>
       </c>
       <c r="E44" t="n">
-        <v>53215.18898912293</v>
+        <v>53215.18509726059</v>
       </c>
       <c r="F44" t="n">
         <v>12258101</v>
@@ -1390,16 +1390,16 @@
         <v>45728</v>
       </c>
       <c r="B48" t="n">
-        <v>54002.1015625</v>
+        <v>54002.09765625</v>
       </c>
       <c r="C48" t="n">
-        <v>54395.5594973816</v>
+        <v>54395.55556267076</v>
       </c>
       <c r="D48" t="n">
-        <v>52723.36327413479</v>
+        <v>52723.35946038251</v>
       </c>
       <c r="E48" t="n">
-        <v>52920.09224157559</v>
+        <v>52920.08841359289</v>
       </c>
       <c r="F48" t="n">
         <v>17973221</v>
@@ -1410,16 +1410,16 @@
         <v>45729</v>
       </c>
       <c r="B49" t="n">
-        <v>53805.37109375</v>
+        <v>53805.375</v>
       </c>
       <c r="C49" t="n">
-        <v>54985.74486545932</v>
+        <v>54985.74885740402</v>
       </c>
       <c r="D49" t="n">
-        <v>53313.54868887112</v>
+        <v>53313.55255941499</v>
       </c>
       <c r="E49" t="n">
-        <v>54887.38038448355</v>
+        <v>54887.38436928702</v>
       </c>
       <c r="F49" t="n">
         <v>24132151</v>
@@ -1430,16 +1430,16 @@
         <v>45730</v>
       </c>
       <c r="B50" t="n">
-        <v>53805.37109375</v>
+        <v>53805.375</v>
       </c>
       <c r="C50" t="n">
-        <v>54198.82901765311</v>
+        <v>54198.83295246801</v>
       </c>
       <c r="D50" t="n">
-        <v>53510.27765082267</v>
+        <v>53510.281535649</v>
       </c>
       <c r="E50" t="n">
-        <v>53608.64213179845</v>
+        <v>53608.64602376599</v>
       </c>
       <c r="F50" t="n">
         <v>10845154</v>
@@ -1450,16 +1450,16 @@
         <v>45733</v>
       </c>
       <c r="B51" t="n">
-        <v>56657.9375</v>
+        <v>56657.94140625</v>
       </c>
       <c r="C51" t="n">
-        <v>56854.66644965278</v>
+        <v>56854.67036946615</v>
       </c>
       <c r="D51" t="n">
-        <v>54493.91905381945</v>
+        <v>54493.9228108724</v>
       </c>
       <c r="E51" t="n">
-        <v>54592.28352864584</v>
+        <v>54592.28729248047</v>
       </c>
       <c r="F51" t="n">
         <v>35559021</v>
@@ -1470,16 +1470,16 @@
         <v>45734</v>
       </c>
       <c r="B52" t="n">
-        <v>56657.9375</v>
+        <v>56657.94140625</v>
       </c>
       <c r="C52" t="n">
-        <v>58035.04014756945</v>
+        <v>58035.04414876302</v>
       </c>
       <c r="D52" t="n">
-        <v>56362.84407552084</v>
+        <v>56362.84796142578</v>
       </c>
       <c r="E52" t="n">
-        <v>57838.31119791667</v>
+        <v>57838.31518554688</v>
       </c>
       <c r="F52" t="n">
         <v>28138594</v>
@@ -1530,16 +1530,16 @@
         <v>45737</v>
       </c>
       <c r="B55" t="n">
-        <v>60690.890625</v>
+        <v>60690.8828125</v>
       </c>
       <c r="C55" t="n">
-        <v>60690.890625</v>
+        <v>60690.8828125</v>
       </c>
       <c r="D55" t="n">
-        <v>59412.15224878444</v>
+        <v>59412.14460089141</v>
       </c>
       <c r="E55" t="n">
-        <v>59903.97470117504</v>
+        <v>59903.96698997164</v>
       </c>
       <c r="F55" t="n">
         <v>40155612</v>
@@ -1550,16 +1550,16 @@
         <v>45740</v>
       </c>
       <c r="B56" t="n">
-        <v>59510.515625</v>
+        <v>59510.51171875</v>
       </c>
       <c r="C56" t="n">
-        <v>60592.525</v>
+        <v>60592.52102272728</v>
       </c>
       <c r="D56" t="n">
-        <v>59510.515625</v>
+        <v>59510.51171875</v>
       </c>
       <c r="E56" t="n">
-        <v>60199.06704545455</v>
+        <v>60199.06309400826</v>
       </c>
       <c r="F56" t="n">
         <v>14088094</v>
@@ -1590,16 +1590,16 @@
         <v>45742</v>
       </c>
       <c r="B58" t="n">
-        <v>60395.79296875</v>
+        <v>60395.796875</v>
       </c>
       <c r="C58" t="n">
-        <v>60395.79296875</v>
+        <v>60395.796875</v>
       </c>
       <c r="D58" t="n">
-        <v>58723.59674648819</v>
+        <v>58723.60054458469</v>
       </c>
       <c r="E58" t="n">
-        <v>58821.96123015065</v>
+        <v>58821.96503460911</v>
       </c>
       <c r="F58" t="n">
         <v>16431645</v>
@@ -1610,16 +1610,16 @@
         <v>45743</v>
       </c>
       <c r="B59" t="n">
-        <v>60789.25390625</v>
+        <v>60789.25</v>
       </c>
       <c r="C59" t="n">
-        <v>60985.98288329288</v>
+        <v>60985.97896440129</v>
       </c>
       <c r="D59" t="n">
-        <v>59805.6090210356</v>
+        <v>59805.60517799353</v>
       </c>
       <c r="E59" t="n">
-        <v>59903.97350955704</v>
+        <v>59903.96966019418</v>
       </c>
       <c r="F59" t="n">
         <v>20389790</v>
